--- a/Result/profitability/8070.xlsx
+++ b/Result/profitability/8070.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.52125</v>
       </c>
       <c r="N2" t="n">
-        <v>17.945</v>
+        <v>17.51125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5487500000000001</v>
+        <v>0.585</v>
       </c>
       <c r="N3" t="n">
-        <v>16.2725</v>
+        <v>16.18875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5275</v>
+        <v>0.56625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.87</v>
+        <v>14.90125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3412500000000001</v>
+        <v>0.4187500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>13.62875</v>
+        <v>13.82375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>0.395</v>
+        <v>0.3850000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>12.4075</v>
+        <v>12.3825</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5225</v>
+        <v>0.67875</v>
       </c>
       <c r="N7" t="n">
-        <v>10.92625</v>
+        <v>11.0475</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>3.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9675</v>
+        <v>1.00125</v>
       </c>
       <c r="N8" t="n">
-        <v>9.7325</v>
+        <v>9.80875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>8.217500000000001</v>
+        <v>8.217499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>1.58625</v>
       </c>
       <c r="N10" t="n">
-        <v>8.188750000000001</v>
+        <v>8.188749999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>2.345</v>
       </c>
       <c r="N12" t="n">
-        <v>7.987500000000001</v>
+        <v>7.9875</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>2.63125</v>
       </c>
       <c r="N13" t="n">
-        <v>7.8</v>
+        <v>7.800000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6129</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4957</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1172</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>729</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.90%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>281</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1010</v>
+      </c>
+      <c r="K75" t="n">
+        <v>550</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.24875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5294117647058825</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6099999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03293736501079914</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.559999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08878770631758681</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
